--- a/docs/curriculum/pnle-comprehensive-review-target-shape.xlsx
+++ b/docs/curriculum/pnle-comprehensive-review-target-shape.xlsx
@@ -573,7 +573,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Proposed 9-plan / 73-section architecture aligned to the PRC 2025 Enhanced Table of Specifications (Nursing Practice I–V). Reshapes the current flat 7-plan, 63-note set. 63 notes stay, 76 are reused from elsewhere in the library, 25 sections still need authoring.</t>
+          <t>Proposed 9-plan / 73-section architecture aligned to the PRC 2025 Enhanced Table of Specifications (Nursing Practice I–V). Reshapes the current flat 7-plan, 63-note set: 63 notes stay, 76 are reused from elsewhere in the library, 25 are newly authored.</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Emergency Assessment, Triage, and ABC Priorities in Nursing</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Prioritization and Clinical Judgement</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -1044,11 +1044,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1127,12 +1123,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Respiratory Emergencies and Mechanical Ventilation in Critical Care Nursing</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -1145,11 +1141,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1197,12 +1189,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Neurologic Emergencies and Acute Neurologic Nursing Care</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
@@ -1215,11 +1207,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1232,12 +1220,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Acute Gastrointestinal, Endocrine, and Renal Emergencies</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
@@ -1250,11 +1238,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1267,12 +1251,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Trauma and Environmental Emergencies in Nursing Care</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -1285,11 +1269,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1302,12 +1282,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>High-Acuity Monitoring, Life-Support Equipment, and Critical Care Nursing</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
@@ -1320,11 +1300,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1962,12 +1938,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Respiratory and Gastrointestinal Pharmacology for Nursing</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Pharmacology</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -1980,11 +1956,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2063,12 +2035,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Psychiatric Pharmacology: Major Drug Classes and Nursing Responsibilities</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Pharmacology</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
@@ -2081,11 +2053,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G32" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2265,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2325,7 +2293,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -2334,21 +2302,21 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>🩺 Foundations, Professional Nursing Practice, and Clinical Judgment</t>
+          <t>❤️ Adult Health Nursing I — Perioperative, Oxygenation, Fluids, Infection, Immunology, and Oncology</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Leadership, Management, and Health Informatics</t>
+          <t>Perioperative Nursing</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Perioperative Nursing: Preoperative, Intraoperative, and Postoperative Care</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2326,17 @@
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>🩺 Foundations, Professional Nursing Practice, and Clinical Judgment</t>
+          <t>❤️ Adult Health Nursing I — Perioperative, Oxygenation, Fluids, Infection, Immunology, and Oncology</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Evidence-Based Practice and Nursing Research</t>
+          <t>Inflammatory and Immunologic Disorders</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Inflammatory, Autoimmune, and Immunologic Disorders in Adult Nursing Care</t>
         </is>
       </c>
     </row>
@@ -2378,17 +2346,17 @@
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>🌏 Community and Public Health Nursing</t>
+          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Foundations of Community Health Nursing and Primary Health Care</t>
+          <t>Nutrition and Metabolic Disorders</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Nutrition Assessment, Therapeutic Diets, and Metabolic Support in Adult Nursing</t>
         </is>
       </c>
     </row>
@@ -2398,17 +2366,17 @@
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>🌏 Community and Public Health Nursing</t>
+          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Community Assessment, Diagnosis, and the Nursing Process</t>
+          <t>Musculoskeletal Disorders</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Musculoskeletal Disorders: Assessment and Nursing Management</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2386,17 @@
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>🌏 Community and Public Health Nursing</t>
+          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Communicable Disease Prevention and Control</t>
+          <t>Sensory: Eye and Ear Disorders</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Eye and Ear Disorders: Assessment and Nursing Management</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2406,17 @@
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>🌏 Community and Public Health Nursing</t>
+          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Family and Population Group Nursing</t>
+          <t>Older Adult and Gerontologic Nursing</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Gerontologic Nursing and Care of Older Adults</t>
         </is>
       </c>
     </row>
@@ -2458,17 +2426,17 @@
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>🌏 Community and Public Health Nursing</t>
+          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Community Organizing, Referral, Records, and Health Technology</t>
+          <t>Respiratory Emergencies and Mechanical Ventilation</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Respiratory Emergencies and Mechanical Ventilation in Critical Care Nursing</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2446,17 @@
       <c r="C12" s="6" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>🤰 Maternal and Newborn Nursing</t>
+          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Reproductive Health and Family Planning</t>
+          <t>Neurologic Emergencies</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Neurologic Emergencies and Acute Neurologic Nursing Care</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2466,17 @@
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>🤰 Maternal and Newborn Nursing</t>
+          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Intrapartum Complications and Obstetric Emergencies</t>
+          <t>Acute GI, Endocrine, and Renal Emergencies</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Acute Gastrointestinal, Endocrine, and Renal Emergencies</t>
         </is>
       </c>
     </row>
@@ -2518,17 +2486,17 @@
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>🧒 Pediatric and Adolescent Nursing</t>
+          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Adolescent Health</t>
+          <t>Trauma and Environmental Emergencies</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Trauma and Environmental Emergencies in Nursing Care</t>
         </is>
       </c>
     </row>
@@ -2538,57 +2506,47 @@
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>❤️ Adult Health Nursing I — Perioperative, Oxygenation, Fluids, Infection, Immunology, and Oncology</t>
+          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Perioperative Nursing</t>
+          <t>High-Acuity Monitoring and Equipment</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>❤️ Adult Health Nursing I — Perioperative, Oxygenation, Fluids, Infection, Immunology, and Oncology</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Inflammatory and Immunologic Disorders</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>(to author)</t>
+          <t>High-Acuity Monitoring, Life-Support Equipment, and Critical Care Nursing</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Community Health Nursing</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
+          <t>🌏 Community and Public Health Nursing</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Nutrition and Metabolic Disorders</t>
+          <t>Foundations of Community Health Nursing and Primary Health Care</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Foundations of Community Health Nursing and Primary Health Care</t>
         </is>
       </c>
     </row>
@@ -2598,17 +2556,17 @@
       <c r="C18" s="6" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
+          <t>🌏 Community and Public Health Nursing</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Musculoskeletal Disorders</t>
+          <t>Community Assessment, Diagnosis, and the Nursing Process</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Community Assessment, Diagnosis, Planning, Intervention, and Evaluation</t>
         </is>
       </c>
     </row>
@@ -2618,17 +2576,17 @@
       <c r="C19" s="6" t="inlineStr"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
+          <t>🌏 Community and Public Health Nursing</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Sensory: Eye and Ear Disorders</t>
+          <t>Communicable Disease Prevention and Control</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Communicable Disease Prevention, Control, Eradication, and Elimination</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2596,17 @@
       <c r="C20" s="6" t="inlineStr"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>🧬 Adult Health Nursing II — Nutrition, GI, Endocrine, Neurologic, Musculoskeletal, and Sensory</t>
+          <t>🌏 Community and Public Health Nursing</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Older Adult and Gerontologic Nursing</t>
+          <t>Family and Population Group Nursing</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Nursing Care of Families and Population Groups in the Community</t>
         </is>
       </c>
     </row>
@@ -2658,57 +2616,47 @@
       <c r="C21" s="6" t="inlineStr"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>🧠 Mental Health and Psychiatric Nursing</t>
+          <t>🌏 Community and Public Health Nursing</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Psychiatric Therapies and Psychopharmacology</t>
+          <t>Community Organizing, Referral, Records, and Health Technology</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Emergency Assessment, Triage, and ABC Priorities</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>(to author)</t>
+          <t>Community Organizing, Referral Systems, Recording, Reporting, and Health Technology</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Maternal and Child Nursing</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
+          <t>🤰 Maternal and Newborn Nursing</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Respiratory Emergencies and Mechanical Ventilation</t>
+          <t>Reproductive Health and Family Planning</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Reproductive Health, Family Planning Methods, and Responsible Parenthood</t>
         </is>
       </c>
     </row>
@@ -2718,57 +2666,47 @@
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
+          <t>🤰 Maternal and Newborn Nursing</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Neurologic Emergencies</t>
+          <t>Intrapartum Complications and Obstetric Emergencies</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Acute GI, Endocrine, and Renal Emergencies</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>(to author)</t>
+          <t>Intrapartum Complications and Obstetric Emergencies</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr"/>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
+          <t>🩺 Foundations, Professional Nursing Practice, and Clinical Judgment</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Trauma and Environmental Emergencies</t>
+          <t>Leadership, Management, and Health Informatics</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Nursing Leadership, Management, and Health Informatics</t>
         </is>
       </c>
     </row>
@@ -2778,57 +2716,157 @@
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>🩺 Foundations, Professional Nursing Practice, and Clinical Judgment</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Evidence-Based Practice and Nursing Research</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Evidence-Based Nursing Practice and Fundamentals of Nursing Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Pharmacology</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>💊 Pharmacology, Medication Management, and Dosage Calculation</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Respiratory and Gastrointestinal Pharmacology</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Respiratory and Gastrointestinal Pharmacology for Nursing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>💊 Pharmacology, Medication Management, and Dosage Calculation</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Psychiatric Pharmacology</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Psychiatric Pharmacology: Major Drug Classes and Nursing Responsibilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Pediatric Nursing</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>🧒 Pediatric and Adolescent Nursing</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Adolescent Health</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Adolescent Growth, Health Promotion, Risk Reduction, and Nursing Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Prioritization and Clinical Judgement</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
           <t>🚨 Emergency, Critical Care, and High-Acuity Nursing</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>High-Acuity Monitoring and Equipment</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>(to author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>💊 Pharmacology, Medication Management, and Dosage Calculation</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Respiratory and Gastrointestinal Pharmacology</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>(to author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>💊 Pharmacology, Medication Management, and Dosage Calculation</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Psychiatric Pharmacology</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>(to author)</t>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Emergency Assessment, Triage, and ABC Priorities</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Emergency Assessment, Triage, and ABC Priorities in Nursing</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Psychiatric – Mental Health Nursing</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>🧠 Mental Health and Psychiatric Nursing</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Psychiatric Therapies and Psychopharmacology</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Psychiatric Therapies and Psychopharmacology in Mental Health Nursing</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2909,7 +2947,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2918,7 +2956,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
@@ -2929,7 +2967,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Clinical Chemistry</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2938,18 +2976,18 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Medicine</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Clinical Chemistry</t>
+          <t>Clinical Pharmacy</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -2958,18 +2996,18 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Clinical Pharmacy</t>
+          <t>Community Health Nursing</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -2978,58 +3016,58 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Community Health Nursing</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>NURSING</t>
+          <t>Exercise Physiology</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>(unset)</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Exercise Physiology</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>(unset)</t>
+          <t>Fluid, Electrolyte, and Acid – Base Balance</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Fluid, Electrolyte, and Acid – Base Balance</t>
+          <t>Fundamentals of Nursing</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -3038,7 +3076,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
@@ -3052,13 +3090,13 @@
           <t>Fundamentals of Nursing</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>NURSING</t>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL_PRACTICE_AND_REGULATION</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -3069,47 +3107,47 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Fundamentals of Nursing</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>PROFESSIONAL_PRACTICE_AND_REGULATION</t>
+          <t>Kinesiology</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>(unset)</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Kinesiology</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>(unset)</t>
+          <t>Maternal and Child Nursing</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Maternal and Child Nursing</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -3118,7 +3156,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
@@ -3129,7 +3167,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Medical – Surgical Nursing</t>
+          <t>Nursing</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3138,7 +3176,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -3149,7 +3187,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Pathophysiology</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -3158,18 +3196,18 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Pathophysiology</t>
+          <t>Patient Safety</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -3178,18 +3216,18 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Patient Safety</t>
+          <t>Pediatric Nursing</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -3198,7 +3236,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
@@ -3209,7 +3247,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Pediatric Nursing</t>
+          <t>Pharmaceutical Calculations</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -3218,18 +3256,18 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Pharmaceutical Calculations</t>
+          <t>Pharmacodynamics</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -3249,7 +3287,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Pharmacodynamics</t>
+          <t>Pharmacokinetics</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -3269,12 +3307,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Pharmacokinetics</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>NURSING</t>
+          <t>Pharmacology</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>(unset)</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -3282,7 +3320,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -3292,24 +3330,24 @@
           <t>Pharmacology</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>(unset)</t>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Nursing · Pharmacy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Pharmacy Practice</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -3318,43 +3356,43 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Nursing · Pharmacy</t>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Pharmacy Practice</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>NURSING</t>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>(unset)</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>(unset)</t>
+          <t>Physiology</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>NURSING</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -3362,14 +3400,14 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Physiology</t>
+          <t>Prioritization and Clinical Judgement</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -3378,7 +3416,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
@@ -3389,7 +3427,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Prioritization and Clinical Judgement</t>
+          <t>Psychiatric – Mental Health Nursing</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -3409,27 +3447,27 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Psychiatric – Mental Health Nursing</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>NURSING</t>
+          <t>Psychology</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>(unset)</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Psychology</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Sports Rehabilitation</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -3442,14 +3480,14 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Psychology</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Sports Rehabilitation</t>
+          <t>Therapeutic Exercise</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -3469,38 +3507,18 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Therapeutic Exercise</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>(unset)</t>
+          <t>Water Treatment</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>ENGINEERING_SCIENCES</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Physical Therapy</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Water Treatment</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>ENGINEERING_SCIENCES</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Biology · Chemical Engineering · Chemistry · Civil Engineering · Environmental Engineering · Sanitary Engineering</t>
         </is>
@@ -5111,12 +5129,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Nursing Leadership, Management, and Health Informatics</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Nursing</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
@@ -5129,11 +5147,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G59" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -5146,12 +5160,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Evidence-Based Nursing Practice and Fundamentals of Nursing Research</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Nursing</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
@@ -5164,11 +5178,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G61" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G61" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5259,12 +5269,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Foundations of Community Health Nursing and Primary Health Care</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Community Health Nursing</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -5277,11 +5287,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5294,12 +5300,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Community Assessment, Diagnosis, Planning, Intervention, and Evaluation</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Community Health Nursing</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
@@ -5312,11 +5318,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5364,12 +5366,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Communicable Disease Prevention, Control, Eradication, and Elimination</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Community Health Nursing</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
@@ -5382,11 +5384,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5465,12 +5463,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Nursing Care of Families and Population Groups in the Community</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Community Health Nursing</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
@@ -5483,11 +5481,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5570,12 +5564,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Community Organizing, Referral Systems, Recording, Reporting, and Health Technology</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Community Health Nursing</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
@@ -5588,11 +5582,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5683,12 +5673,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Reproductive Health, Family Planning Methods, and Responsible Parenthood</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Maternal and Child Nursing</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -5701,11 +5691,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6040,12 +6026,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Intrapartum Complications and Obstetric Emergencies</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Maternal and Child Nursing</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
@@ -6058,11 +6044,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6813,12 +6795,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Adolescent Growth, Health Promotion, Risk Reduction, and Nursing Care</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Pediatric Nursing</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -6831,11 +6813,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6926,12 +6904,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Perioperative Nursing: Preoperative, Intraoperative, and Postoperative Care</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -6944,11 +6922,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7814,12 +7788,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Inflammatory, Autoimmune, and Immunologic Disorders in Adult Nursing Care</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -7832,11 +7806,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7962,12 +7932,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Nutrition Assessment, Therapeutic Diets, and Metabolic Support in Adult Nursing</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -7980,11 +7950,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8164,12 +8130,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Musculoskeletal Disorders: Assessment and Nursing Management</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E15" s="16" t="inlineStr">
@@ -8182,11 +8148,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8199,12 +8161,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Eye and Ear Disorders: Assessment and Nursing Management</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -8217,11 +8179,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8234,12 +8192,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Gerontologic Nursing and Care of Older Adults</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Medical – Surgical Nursing</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
@@ -8252,11 +8210,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G19" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8658,12 +8612,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>(to author)</t>
+          <t>Psychiatric Therapies and Psychopharmacology in Mental Health Nursing</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>(to decide)</t>
+          <t>Psychiatric – Mental Health Nursing</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
@@ -8676,11 +8630,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>same canonical note in another plan — do not duplicate</t>
-        </is>
-      </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/curriculum/pnle-comprehensive-review-target-shape.xlsx
+++ b/docs/curriculum/pnle-comprehensive-review-target-shape.xlsx
@@ -952,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -962,6 +962,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1014,6 +1015,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1045,6 +1051,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1078,6 +1089,11 @@
       <c r="G7" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -1111,6 +1127,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1142,6 +1163,11 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1177,6 +1203,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1208,6 +1239,11 @@
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1239,6 +1275,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1270,6 +1311,11 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1301,6 +1347,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1317,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1327,6 +1378,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1379,6 +1431,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1412,6 +1469,11 @@
       <c r="G5" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -1445,6 +1507,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -1476,6 +1543,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -1507,6 +1579,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -1538,6 +1615,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -1569,6 +1651,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1602,6 +1689,11 @@
       <c r="G12" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -1635,6 +1727,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -1666,6 +1763,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -1697,6 +1799,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1730,6 +1837,11 @@
       <c r="G17" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
@@ -1763,6 +1875,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1796,6 +1913,11 @@
       <c r="G20" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -1829,6 +1951,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -1860,6 +1987,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1893,6 +2025,11 @@
       <c r="G24" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -1926,6 +2063,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1957,6 +2099,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1990,6 +2137,11 @@
       <c r="G29" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2023,6 +2175,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2054,6 +2211,11 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2087,6 +2249,11 @@
       <c r="G34" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2120,6 +2287,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -2151,6 +2323,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -2182,6 +2359,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2215,6 +2397,11 @@
       <c r="G39" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2429,7 @@
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2289,6 +2477,11 @@
           <t>Note title</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2317,6 +2510,11 @@
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Perioperative Nursing: Preoperative, Intraoperative, and Postoperative Care</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2339,6 +2537,11 @@
           <t>Inflammatory, Autoimmune, and Immunologic Disorders in Adult Nursing Care</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -2359,6 +2562,11 @@
           <t>Nutrition Assessment, Therapeutic Diets, and Metabolic Support in Adult Nursing</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -2379,6 +2587,11 @@
           <t>Musculoskeletal Disorders: Assessment and Nursing Management</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -2399,6 +2612,11 @@
           <t>Eye and Ear Disorders: Assessment and Nursing Management</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -2419,6 +2637,11 @@
           <t>Gerontologic Nursing and Care of Older Adults</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -2439,6 +2662,11 @@
           <t>Respiratory Emergencies and Mechanical Ventilation in Critical Care Nursing</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -2459,6 +2687,11 @@
           <t>Neurologic Emergencies and Acute Neurologic Nursing Care</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -2479,6 +2712,11 @@
           <t>Acute Gastrointestinal, Endocrine, and Renal Emergencies</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -2499,6 +2737,11 @@
           <t>Trauma and Environmental Emergencies in Nursing Care</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -2519,6 +2762,11 @@
           <t>High-Acuity Monitoring, Life-Support Equipment, and Critical Care Nursing</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -2547,6 +2795,11 @@
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Foundations of Community Health Nursing and Primary Health Care</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2569,6 +2822,11 @@
           <t>Community Assessment, Diagnosis, Planning, Intervention, and Evaluation</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -2589,6 +2847,11 @@
           <t>Communicable Disease Prevention, Control, Eradication, and Elimination</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -2609,6 +2872,11 @@
           <t>Nursing Care of Families and Population Groups in the Community</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -2629,6 +2897,11 @@
           <t>Community Organizing, Referral Systems, Recording, Reporting, and Health Technology</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2657,6 +2930,11 @@
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Reproductive Health, Family Planning Methods, and Responsible Parenthood</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2679,6 +2957,11 @@
           <t>Intrapartum Complications and Obstetric Emergencies</t>
         </is>
       </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -2707,6 +2990,11 @@
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Nursing Leadership, Management, and Health Informatics</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2729,6 +3017,11 @@
           <t>Evidence-Based Nursing Practice and Fundamentals of Nursing Research</t>
         </is>
       </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2757,6 +3050,11 @@
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Respiratory and Gastrointestinal Pharmacology for Nursing</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -2779,6 +3077,11 @@
           <t>Psychiatric Pharmacology: Major Drug Classes and Nursing Responsibilities</t>
         </is>
       </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2809,6 +3112,11 @@
           <t>Adolescent Growth, Health Promotion, Risk Reduction, and Nursing Care</t>
         </is>
       </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2839,6 +3147,11 @@
           <t>Emergency Assessment, Triage, and ABC Priorities in Nursing</t>
         </is>
       </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2867,6 +3180,11 @@
       <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Psychiatric Therapies and Psychopharmacology in Mental Health Nursing</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3658,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Nursing · Pharmacy</t>
+          <t>Nursing, Pharmacy</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3838,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Biology · Chemical Engineering · Chemistry · Civil Engineering · Environmental Engineering · Sanitary Engineering</t>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3550,6 +3868,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3602,6 +3921,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3635,6 +3959,11 @@
       <c r="G5" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -3668,6 +3997,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -3699,6 +4033,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -3730,6 +4069,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -3761,6 +4105,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -3792,6 +4141,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -3823,6 +4177,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
@@ -3854,6 +4213,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Psychology</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr"/>
@@ -3885,6 +4249,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
@@ -3916,6 +4285,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -3947,6 +4321,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -3978,6 +4357,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -4009,6 +4393,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -4036,6 +4425,11 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr"/>
@@ -4063,6 +4457,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
@@ -4090,6 +4489,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -4117,6 +4521,11 @@
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -4144,6 +4553,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -4171,6 +4585,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Biology, Chemical Engineering, Chemistry, Civil Engineering, Environmental Engineering, Sanitary Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -4204,6 +4623,11 @@
       <c r="G25" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -4237,6 +4661,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -4268,6 +4697,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -4299,6 +4733,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -4330,6 +4769,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -4361,6 +4805,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
@@ -4392,6 +4841,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -4423,6 +4877,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -4454,6 +4913,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
@@ -4485,6 +4949,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr"/>
@@ -4516,6 +4985,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
@@ -4547,6 +5021,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr"/>
@@ -4578,6 +5057,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
@@ -4609,6 +5093,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -4642,6 +5131,11 @@
       <c r="G40" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -4675,6 +5169,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -4708,6 +5207,11 @@
       <c r="G43" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -4741,6 +5245,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr"/>
@@ -4772,6 +5281,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -4805,6 +5319,11 @@
       <c r="G47" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -4838,6 +5357,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr"/>
@@ -4869,6 +5393,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
@@ -4900,6 +5429,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr"/>
@@ -4931,6 +5465,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr"/>
@@ -4962,6 +5501,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr"/>
@@ -4993,6 +5537,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
@@ -5024,6 +5573,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr"/>
@@ -5055,6 +5609,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
@@ -5086,6 +5645,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr"/>
@@ -5117,6 +5681,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -5148,6 +5717,11 @@
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -5179,6 +5753,11 @@
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5195,7 +5774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5205,6 +5784,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5257,6 +5837,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5288,6 +5873,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5319,6 +5909,11 @@
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5354,6 +5949,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5385,6 +5985,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5418,6 +6023,11 @@
       <c r="G13" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -5451,6 +6061,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -5482,6 +6097,11 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5517,6 +6137,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5552,6 +6177,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5583,6 +6213,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5599,7 +6234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5609,6 +6244,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5661,6 +6297,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5692,6 +6333,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5725,6 +6371,11 @@
       <c r="G7" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -5758,6 +6409,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -5791,6 +6447,11 @@
       <c r="G10" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -5824,6 +6485,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5857,6 +6523,11 @@
       <c r="G13" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -5890,6 +6561,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -5921,6 +6597,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -5952,6 +6633,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -5983,6 +6669,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
@@ -6014,6 +6705,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -6045,6 +6741,11 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6078,6 +6779,11 @@
       <c r="G22" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6111,6 +6817,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -6142,6 +6853,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -6173,6 +6889,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6208,6 +6929,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6241,6 +6967,11 @@
       <c r="G29" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6272,6 +7003,11 @@
       <c r="G30" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6290,7 +7026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6300,6 +7036,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6352,6 +7089,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6385,6 +7127,11 @@
       <c r="G5" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6418,6 +7165,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr"/>
@@ -6449,6 +7201,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
@@ -6480,6 +7237,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -6511,6 +7273,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -6546,6 +7313,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6579,6 +7351,11 @@
       <c r="G13" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6612,6 +7389,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6647,6 +7429,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -6680,6 +7467,11 @@
       <c r="G18" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6713,6 +7505,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -6748,6 +7545,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -6783,6 +7585,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -6814,6 +7621,11 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6830,7 +7642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6840,6 +7652,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6892,6 +7705,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6923,6 +7741,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6956,6 +7779,11 @@
       <c r="G7" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -6989,6 +7817,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr"/>
@@ -7020,6 +7853,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
@@ -7051,6 +7889,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr"/>
@@ -7082,6 +7925,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7115,6 +7963,11 @@
       <c r="G13" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -7148,6 +8001,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr"/>
@@ -7179,6 +8037,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
@@ -7210,6 +8073,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr"/>
@@ -7241,6 +8109,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7274,6 +8147,11 @@
       <c r="G19" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -7307,6 +8185,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr"/>
@@ -7338,6 +8221,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
@@ -7369,6 +8257,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr"/>
@@ -7400,6 +8293,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
@@ -7431,6 +8329,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr"/>
@@ -7462,6 +8365,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
@@ -7493,6 +8401,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr"/>
@@ -7524,6 +8437,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
@@ -7555,6 +8473,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr"/>
@@ -7586,6 +8509,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
@@ -7617,6 +8545,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr"/>
@@ -7648,6 +8581,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
@@ -7679,6 +8617,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr"/>
@@ -7710,6 +8653,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7743,6 +8691,11 @@
       <c r="G35" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
@@ -7776,6 +8729,11 @@
           <t>unset requires a SINGLE applicable program</t>
         </is>
       </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Physical Therapy</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7807,6 +8765,11 @@
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7840,6 +8803,11 @@
       <c r="G40" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -7858,7 +8826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7868,6 +8836,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7920,6 +8889,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7951,6 +8925,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7984,6 +8963,11 @@
       <c r="G7" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -8017,6 +9001,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8052,6 +9041,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8085,6 +9079,11 @@
       <c r="G12" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -8118,6 +9117,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8149,6 +9153,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8180,6 +9189,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8211,6 +9225,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8227,7 +9246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8237,6 +9256,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8289,6 +9309,11 @@
           <t>Flags</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Applicable Programs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8324,6 +9349,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8359,6 +9389,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -8394,6 +9429,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -8429,6 +9469,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -8464,6 +9509,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8499,6 +9549,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8534,6 +9589,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8567,6 +9627,11 @@
       <c r="G19" s="18" t="inlineStr">
         <is>
           <t>context already set — verify before changing</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
         </is>
       </c>
     </row>
@@ -8600,6 +9665,11 @@
           <t>context already set — verify before changing</t>
         </is>
       </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8631,6 +9701,11 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
